--- a/product_selector_out/STM32L4x3 - diff.xlsx
+++ b/product_selector_out/STM32L4x3 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,21 +48,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B7E1CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -94,9 +79,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -555,7 +537,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -615,7 +597,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -625,7 +607,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -635,7 +617,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="18">
@@ -700,22 +682,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -727,39 +705,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L443RC</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.71 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -767,16 +741,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L443RC</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -790,7 +764,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -799,7 +773,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L443RC</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -813,7 +787,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -822,7 +796,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32L443VC</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -849,71 +823,63 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L443VC</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L443VC</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L443VC</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.71 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -921,16 +887,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L443VC</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -944,7 +910,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -953,7 +919,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L443VC</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -967,7 +933,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -976,7 +942,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1003,71 +969,63 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.71 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1075,16 +1033,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1098,7 +1056,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1107,7 +1065,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1121,7 +1079,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1130,7 +1088,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1157,71 +1115,63 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L433RC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.71 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1229,16 +1179,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L433RC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1252,7 +1202,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1261,7 +1211,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L433RC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1275,630 +1225,14 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>STM32L433RB</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>STM32L433RB</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>STM32L433RB</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>STM32L433RB</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1.71 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>STM32L433RB</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>STM32L433RB</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>STM32L443CC</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>STM32L443CC</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>STM32L443CC</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>STM32L443CC</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1.71 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>STM32L443CC</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>STM32L443CC</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32L433CC</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>STM32L433CC</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>STM32L433CC</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>STM32L433CC</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1.71 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>STM32L433CC</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>STM32L433CC</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>STM32L433RC</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>STM32L433RC</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>STM32L433RC</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>STM32L433RC</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1.71 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>STM32L433RC</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>STM32L433RC</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E66"/>
+  <autoFilter ref="A18:E42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32L4x3 - diff.xlsx
+++ b/product_selector_out/STM32L4x3 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B7E1CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -71,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -79,6 +94,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -537,7 +555,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -547,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -597,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -607,7 +625,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -617,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>488</v>
+        <v>475</v>
       </c>
     </row>
     <row r="18">
@@ -655,22 +673,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>BLANK_FILLED</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -682,18 +700,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -705,25 +727,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L443VC</t>
+          <t>STM32L443RC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -741,7 +767,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>BLANK_FILLED</t>
         </is>
@@ -750,7 +776,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L443VC</t>
+          <t>STM32L443RC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -764,7 +790,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -773,7 +799,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L443VC</t>
+          <t>STM32L443RC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -787,7 +813,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -796,80 +822,88 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>BLANK_FILLED</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -887,7 +921,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>BLANK_FILLED</t>
         </is>
@@ -896,7 +930,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -910,7 +944,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -919,7 +953,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -933,7 +967,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -942,80 +976,88 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>BLANK_FILLED</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1033,7 +1075,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>BLANK_FILLED</t>
         </is>
@@ -1042,7 +1084,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1056,7 +1098,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1065,7 +1107,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1079,7 +1121,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1088,85 +1130,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>BLANK_FILLED</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L433RC</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1179,7 +1229,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>BLANK_FILLED</t>
         </is>
@@ -1188,51 +1238,1018 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L433RC</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10||11</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>STM32L433CB</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>10, 11</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>STM32L433CB</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>10||11 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>STM32L433CB</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STM32L433CB</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>STM32L433CB</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>STM32L433RB</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>STM32L433RB</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>STM32L433RB</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>STM32L433RB</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>STM32L433RB</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>STM32L433RB</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>STM32L443CC</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>STM32L443CC</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32L443CC</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>STM32L443CC</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>10||11</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>STM32L443CC</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>10, 11</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>STM32L443CC</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>10||11 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>STM32L443CC</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>STM32L443CC</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>STM32L443CC</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>STM32L433CC</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>STM32L433CC</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>STM32L433CC</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>STM32L433CC</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>10||11</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>STM32L433CC</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>10, 11</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>STM32L433CC</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>10||11 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>STM32L433CC</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>STM32L433CC</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>STM32L433CC</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>STM32L433RC</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>15||16</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>15, 16</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>15||16 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
         <is>
           <t>Longevity Starting Date</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
         <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E42"/>
+  <autoFilter ref="A18:E79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32L4x3 - diff.xlsx
+++ b/product_selector_out/STM32L4x3 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="18">
@@ -754,22 +754,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>BLANK_FILLED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -781,16 +777,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -799,23 +795,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L443RC</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -840,9 +840,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -867,9 +867,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -881,22 +881,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -908,68 +904,72 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>BLANK_FILLED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L443VC</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L443VC</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -994,9 +994,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1008,22 +1008,18 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1035,95 +1031,99 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1135,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -1162,22 +1162,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10||11</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1189,22 +1189,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>10, 11</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1216,22 +1216,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10||11 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1243,22 +1243,18 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>10||11</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1270,120 +1266,120 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>10, 11</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>10||11 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1397,29 +1393,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1437,16 +1429,16 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1456,7 +1448,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1464,82 +1456,90 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>10||11</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>10, 11</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1551,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10||11 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1578,22 +1578,18 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1605,44 +1601,40 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10||11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -1654,22 +1646,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>10, 11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -1681,22 +1673,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>10||11 (workbook and API agree)</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -1708,73 +1700,81 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10||11</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>10, 11</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>10||11 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,18 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1813,29 +1809,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L433RC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1845,7 +1837,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1853,70 +1845,70 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L433RC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>10||11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L433RC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>10, 11</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L433RC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1926,88 +1918,92 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>10||11 (workbook and API agree)</t>
+          <t>15||16</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L433RC</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15, 16</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L433RC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>15||16 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L433RC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2021,235 +2017,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>STM32L433RC</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>STM32L433RC</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>STM32L433RC</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>15||16</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>STM32L433RC</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>15, 16</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>STM32L433RC</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>15||16 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>STM32L433RC</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>STM32L433RC</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>STM32L433RC</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A18:E79"/>
+  <autoFilter ref="A18:E71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32L4x3 - diff.xlsx
+++ b/product_selector_out/STM32L4x3 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="6">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -795,27 +795,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L443VC</t>
+          <t>STM32L443RC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -840,9 +836,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -859,7 +855,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -867,9 +863,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -881,18 +877,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -904,13 +904,13 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -922,54 +922,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -986,7 +978,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -994,9 +986,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1008,18 +1000,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1031,99 +1027,91 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1123,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1162,22 +1150,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10||11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1189,22 +1177,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10, 11</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1216,22 +1204,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>A/D Converters 12-bit | Number of A/D Converters typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>10||11 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -1243,18 +1231,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10||11</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1266,117 +1258,113 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>10, 11</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10||11 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -1393,25 +1381,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1429,16 +1421,16 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1448,7 +1440,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1456,90 +1448,78 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>10||11</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>10, 11</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1531,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10||11 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1578,18 +1558,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1601,40 +1585,44 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10||11</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -1646,22 +1634,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10, 11</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -1673,22 +1661,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>10||11 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -1700,81 +1688,69 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>10||11</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>10, 11</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>10||11 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1786,18 +1762,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1809,25 +1789,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L433RC</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1837,7 +1821,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1845,70 +1829,70 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L433RC</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10||11</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L433RC</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>10, 11</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L433RC</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1918,89 +1902,81 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>15||16</t>
+          <t>10||11 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L433RC</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>15, 16</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L433RC</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>15||16 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L433RC</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2017,23 +1993,231 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>15||16</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>15, 16</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>15||16 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>Longevity Starting Date</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr">
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
         <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E71"/>
+  <autoFilter ref="A18:E79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>